--- a/cet4/result/84_修仙少女_逆天改命的女帝/84_修仙少女_逆天改命的女帝_学习版.xlsx
+++ b/cet4/result/84_修仙少女_逆天改命的女帝/84_修仙少女_逆天改命的女帝_学习版.xlsx
@@ -399,710 +399,710 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>ball</v>
       </c>
       <c r="B2" t="str">
-        <v>ball</v>
+        <v>/bɔːl/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>舞会</v>
       </c>
-      <c r="D2" t="str">
-        <v>ball(舞会)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>rely</v>
       </c>
       <c r="B3" t="str">
-        <v>rely</v>
+        <v>/rɪˈlaɪ/</v>
       </c>
       <c r="C3" t="str">
+        <v>vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>依靠</v>
       </c>
-      <c r="D3" t="str">
-        <v>rely(依靠)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>reliability</v>
       </c>
       <c r="B4" t="str">
-        <v>reliability</v>
+        <v>/rɪˌlaɪəˈbɪləti/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>可靠性</v>
       </c>
-      <c r="D4" t="str">
-        <v>reliability(可靠性)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>dissolve</v>
       </c>
       <c r="B5" t="str">
-        <v>dissolve</v>
+        <v>/dɪˈzɑːlv/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>溶解</v>
       </c>
-      <c r="D5" t="str">
-        <v>dissolve(溶解)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>attain</v>
       </c>
       <c r="B6" t="str">
-        <v>attain</v>
+        <v>/əˈteɪn/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>达到</v>
       </c>
-      <c r="D6" t="str">
-        <v>attain(达到)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>solely</v>
       </c>
       <c r="B7" t="str">
-        <v>solely</v>
+        <v>/ˈsoʊlli/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>仅仅</v>
       </c>
-      <c r="D7" t="str">
-        <v>solely(仅仅)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>someone</v>
       </c>
       <c r="B8" t="str">
-        <v>someone</v>
+        <v>/ˈsʌmwʌn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D8" t="str">
         <v>有人</v>
       </c>
-      <c r="D8" t="str">
-        <v>someone(有人)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>insufficient</v>
       </c>
       <c r="B9" t="str">
-        <v>insufficient</v>
+        <v>/ˌɪnsəˈfɪʃnt/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>不足的</v>
       </c>
-      <c r="D9" t="str">
-        <v>insufficient(不足的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>turn</v>
       </c>
       <c r="B10" t="str">
-        <v>turn</v>
+        <v>/tɜːrn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>转变</v>
       </c>
-      <c r="D10" t="str">
-        <v>turn(转变)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>unsatisfactory</v>
       </c>
       <c r="B11" t="str">
-        <v>unsatisfactory</v>
+        <v>/ˌʌnˌsætɪsˈfæktəri/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>不令人满意的</v>
       </c>
-      <c r="D11" t="str">
-        <v>unsatisfactory(不令人满意的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>relieve</v>
       </c>
       <c r="B12" t="str">
-        <v>relieve</v>
+        <v>/rɪˈliːv/</v>
       </c>
       <c r="C12" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>减轻</v>
       </c>
-      <c r="D12" t="str">
-        <v>relieve(减轻)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>warn</v>
       </c>
       <c r="B13" t="str">
-        <v>warn</v>
+        <v>/wɔːrn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>警告</v>
       </c>
-      <c r="D13" t="str">
-        <v>warn(警告)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>tidy</v>
       </c>
       <c r="B14" t="str">
-        <v>tidy</v>
+        <v>/ˈtaɪdi/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>整齐</v>
       </c>
-      <c r="D14" t="str">
-        <v>tidy(整齐)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>bristle</v>
       </c>
       <c r="B15" t="str">
-        <v>bristle</v>
+        <v>/ˈbrɪsl/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D15" t="str">
         <v>刚毛</v>
       </c>
-      <c r="D15" t="str">
-        <v>bristle(刚毛)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>jolly</v>
       </c>
       <c r="B16" t="str">
-        <v>jolly</v>
+        <v>/ˈdʒɑːli/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>快乐的</v>
       </c>
-      <c r="D16" t="str">
-        <v>jolly(快乐的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>purity</v>
       </c>
       <c r="B17" t="str">
-        <v>purity</v>
+        <v>/ˈpjʊrəti/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>纯净</v>
       </c>
-      <c r="D17" t="str">
-        <v>purity(纯净)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>Thursday</v>
       </c>
       <c r="B18" t="str">
-        <v>Thursday</v>
+        <v>/'θɜːrzdei/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>星期四</v>
       </c>
-      <c r="D18" t="str">
-        <v>Thursday(星期四)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>bargain</v>
       </c>
       <c r="B19" t="str">
-        <v>bargain</v>
+        <v>/ˈbɑːrɡən/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>机会</v>
       </c>
-      <c r="D19" t="str">
-        <v>bargain(机会)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>winner</v>
       </c>
       <c r="B20" t="str">
-        <v>winner</v>
+        <v>/ˈwɪnər/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>获胜者</v>
       </c>
-      <c r="D20" t="str">
-        <v>winner(获胜者)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>easy</v>
       </c>
       <c r="B21" t="str">
-        <v>easy</v>
+        <v>/ˈiːzi/</v>
       </c>
       <c r="C21" t="str">
+        <v>vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>容易的</v>
       </c>
-      <c r="D21" t="str">
-        <v>easy(容易的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>chemist</v>
       </c>
       <c r="B22" t="str">
-        <v>chemist</v>
+        <v>/ˈkemɪst/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>炼金术士</v>
       </c>
-      <c r="D22" t="str">
-        <v>chemist(炼金术士)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>possess</v>
       </c>
       <c r="B23" t="str">
-        <v>possess</v>
+        <v>/pəˈzes/</v>
       </c>
       <c r="C23" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D23" t="str">
         <v>拥有</v>
       </c>
-      <c r="D23" t="str">
-        <v>possess(拥有)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>altogether</v>
       </c>
       <c r="B24" t="str">
-        <v>altogether</v>
+        <v>/ˌɔːltəˈɡeðər/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>完全</v>
       </c>
-      <c r="D24" t="str">
-        <v>altogether(完全)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>unfortunately</v>
       </c>
       <c r="B25" t="str">
-        <v>unfortunately</v>
+        <v>/ʌnˈfɔːrtʃənətli/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D25" t="str">
         <v>不幸地</v>
       </c>
-      <c r="D25" t="str">
-        <v>unfortunately(不幸地)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>ashamed</v>
       </c>
       <c r="B26" t="str">
-        <v>ashamed</v>
+        <v>/əˈʃeɪmd/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>羞愧</v>
       </c>
-      <c r="D26" t="str">
-        <v>ashamed(羞愧)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>farewell</v>
       </c>
       <c r="B27" t="str">
-        <v>farewell</v>
+        <v>/ˌferˈwel/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./adj./int.</v>
+      </c>
+      <c r="D27" t="str">
         <v>告别</v>
       </c>
-      <c r="D27" t="str">
-        <v>farewell(告别)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>harvest</v>
       </c>
       <c r="B28" t="str">
-        <v>harvest</v>
+        <v>/ˈhɑːrvɪst/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D28" t="str">
         <v>收获</v>
       </c>
-      <c r="D28" t="str">
-        <v>harvest(收获)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>require</v>
       </c>
       <c r="B29" t="str">
-        <v>require</v>
+        <v>/rɪˈkwaɪər/</v>
       </c>
       <c r="C29" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D29" t="str">
         <v>需要</v>
       </c>
-      <c r="D29" t="str">
-        <v>require(需要)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>deserve</v>
       </c>
       <c r="B30" t="str">
-        <v>deserve</v>
+        <v>/dɪˈzɜːrv/</v>
       </c>
       <c r="C30" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D30" t="str">
         <v>应得</v>
       </c>
-      <c r="D30" t="str">
-        <v>deserve(应得)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>unit</v>
       </c>
       <c r="B31" t="str">
-        <v>unit</v>
+        <v>/ˈjuːnɪt/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>单元</v>
       </c>
-      <c r="D31" t="str">
-        <v>unit(单元)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>meet</v>
       </c>
       <c r="B32" t="str">
-        <v>meet</v>
+        <v>/miːt/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>相遇</v>
       </c>
-      <c r="D32" t="str">
-        <v>meet(相遇)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>component</v>
       </c>
       <c r="B33" t="str">
-        <v>component</v>
+        <v>/kəmˈpoʊnənt/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>组成部分</v>
       </c>
-      <c r="D33" t="str">
-        <v>component(组成部分)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>weary</v>
       </c>
       <c r="B34" t="str">
-        <v>weary</v>
+        <v>/ˈwɪri/</v>
       </c>
       <c r="C34" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>疲倦</v>
       </c>
-      <c r="D34" t="str">
-        <v>weary(疲倦)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>liberty</v>
       </c>
       <c r="B35" t="str">
-        <v>liberty</v>
+        <v>/ˈlɪbərti/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>自由</v>
       </c>
-      <c r="D35" t="str">
-        <v>liberty(自由)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>tent</v>
       </c>
       <c r="B36" t="str">
-        <v>tent</v>
+        <v>/tent/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D36" t="str">
         <v>帐篷</v>
       </c>
-      <c r="D36" t="str">
-        <v>tent(帐篷)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>publish</v>
       </c>
       <c r="B37" t="str">
-        <v>publish</v>
+        <v>/ˈpʌblɪʃ/</v>
       </c>
       <c r="C37" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D37" t="str">
         <v>发表</v>
       </c>
-      <c r="D37" t="str">
-        <v>publish(发表)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>pour</v>
       </c>
       <c r="B38" t="str">
-        <v>pour</v>
+        <v>/pɔːr/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D38" t="str">
         <v>倾泻</v>
       </c>
-      <c r="D38" t="str">
-        <v>pour(倾泻)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>moist</v>
       </c>
       <c r="B39" t="str">
-        <v>moist</v>
+        <v>/mɔɪst/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>潮湿</v>
       </c>
-      <c r="D39" t="str">
-        <v>moist(潮湿)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>frost</v>
       </c>
       <c r="B40" t="str">
-        <v>frost</v>
+        <v>/frɔːst/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D40" t="str">
         <v>霜</v>
       </c>
-      <c r="D40" t="str">
-        <v>frost(霜)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>successful</v>
       </c>
       <c r="B41" t="str">
-        <v>successful</v>
+        <v>/səkˈsesfl/</v>
       </c>
       <c r="C41" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>成功的</v>
       </c>
-      <c r="D41" t="str">
-        <v>successful(成功的)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>thirst</v>
       </c>
       <c r="B42" t="str">
-        <v>thirst</v>
+        <v>/θɜːrst/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>渴望</v>
       </c>
-      <c r="D42" t="str">
-        <v>thirst(渴望)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>mercury</v>
       </c>
       <c r="B43" t="str">
-        <v>mercury</v>
+        <v>/ˈmɜːrkjəri/</v>
       </c>
       <c r="C43" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>水银</v>
       </c>
-      <c r="D43" t="str">
-        <v>mercury(水银)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>considerable</v>
       </c>
       <c r="B44" t="str">
-        <v>considerable</v>
+        <v>/kənˈsɪdərəbl/</v>
       </c>
       <c r="C44" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D44" t="str">
         <v>相当大的</v>
       </c>
-      <c r="D44" t="str">
-        <v>considerable(相当大的)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>cabin</v>
       </c>
       <c r="B45" t="str">
-        <v>cabin</v>
+        <v>/ˈkæbɪn/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D45" t="str">
         <v>小屋</v>
       </c>
-      <c r="D45" t="str">
-        <v>cabin(小屋)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>compose</v>
       </c>
       <c r="B46" t="str">
-        <v>compose</v>
+        <v>/kəmˈpoʊz/</v>
       </c>
       <c r="C46" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D46" t="str">
         <v>组成</v>
       </c>
-      <c r="D46" t="str">
-        <v>compose(组成)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>give</v>
       </c>
       <c r="B47" t="str">
-        <v>give</v>
+        <v>/ɡɪv/</v>
       </c>
       <c r="C47" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D47" t="str">
         <v>给</v>
       </c>
-      <c r="D47" t="str">
-        <v>give(给)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>heavily</v>
       </c>
       <c r="B48" t="str">
-        <v>heavily</v>
+        <v>/ˈhevɪli/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D48" t="str">
         <v>严重</v>
       </c>
-      <c r="D48" t="str">
-        <v>heavily(严重)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>border</v>
       </c>
       <c r="B49" t="str">
-        <v>border</v>
+        <v>/ˈbɔːrdər/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D49" t="str">
         <v>边界</v>
       </c>
-      <c r="D49" t="str">
-        <v>border(边界)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>slope</v>
       </c>
       <c r="B50" t="str">
-        <v>slope</v>
+        <v>/sloʊp/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D50" t="str">
         <v>斜坡</v>
-      </c>
-      <c r="D50" t="str">
-        <v>slope(斜坡)📢</v>
       </c>
     </row>
   </sheetData>
